--- a/questionnaire_templates/030_financial_services_pre_employment_assessment_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/030_financial_services_pre_employment_assessment_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1160,17 +1160,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>financial_services_pre_employment_assessment_questionnaire_question_1_choices</t>
+          <t>financial_services_pre_employment_assessment_questionnaire_question_5_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>financial_services_and_products</t>
+          <t>financial_markets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Financial services and products</t>
+          <t>Financial Markets</t>
         </is>
       </c>
     </row>
@@ -1187,41 +1187,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Financial Markets</t>
+          <t>Financial markets</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>financial_services_pre_employment_assessment_questionnaire_question_5_choices</t>
+          <t>financial_services_pre_employment_assessment_questionnaire_question_7_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>financial_markets</t>
+          <t>financial_services</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Financial Markets</t>
+          <t>Financial services</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>financial_services_pre_employment_assessment_questionnaire_question_5_choices</t>
+          <t>financial_services_pre_employment_assessment_questionnaire_question_7_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>financial_markets</t>
+          <t>financial_products</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Financial markets</t>
+          <t>Financial products</t>
         </is>
       </c>
     </row>
@@ -1238,41 +1238,41 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Financial services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>financial_services_pre_employment_assessment_questionnaire_question_7_choices</t>
+          <t>financial_services_pre_employment_assessment_questionnaire_question_10_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>financial_products</t>
+          <t>financial_services</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financial products</t>
+          <t>Financial services</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>financial_services_pre_employment_assessment_questionnaire_question_7_choices</t>
+          <t>financial_services_pre_employment_assessment_questionnaire_question_10_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>financial_services</t>
+          <t>financial_products</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Financial products</t>
         </is>
       </c>
     </row>
@@ -1289,41 +1289,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Financial services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>financial_services_pre_employment_assessment_questionnaire_question_10_choices</t>
+          <t>financial_services_pre_employment_assessment_questionnaire_question_14_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>financial_products</t>
+          <t>financial_markets</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Financial products</t>
+          <t>Financial markets</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>financial_services_pre_employment_assessment_questionnaire_question_10_choices</t>
+          <t>financial_services_pre_employment_assessment_questionnaire_question_14_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>financial_services</t>
+          <t>financial_products</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Financial products</t>
         </is>
       </c>
     </row>
@@ -1335,87 +1335,87 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>financial_markets</t>
+          <t>financial_services</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Financial markets</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>financial_services_pre_employment_assessment_questionnaire_question_14_choices</t>
+          <t>financial_services_pre_employment_assessment_questionnaire_question_18_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>financial_products</t>
+          <t>financial_services</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Financial products</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>financial_services_pre_employment_assessment_questionnaire_question_14_choices</t>
+          <t>financial_services_pre_employment_assessment_questionnaire_question_18_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>financial_services</t>
+          <t>financial_products</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Financial products</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>financial_services_pre_employment_assessment_questionnaire_question_18_choices</t>
+          <t>financial_services_pre_employment_assessment_questionnaire_question_19_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>financial_services</t>
+          <t>financial_markets</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Financial markets</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>financial_services_pre_employment_assessment_questionnaire_question_18_choices</t>
+          <t>financial_services_pre_employment_assessment_questionnaire_question_19_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>financial_products</t>
+          <t>financial_services</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Financial products</t>
+          <t>Financial services</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>financial_services_pre_employment_assessment_questionnaire_question_18_choices</t>
+          <t>financial_services_pre_employment_assessment_questionnaire_question_19_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1424,57 +1424,6 @@
         </is>
       </c>
       <c r="C19" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>financial_services_pre_employment_assessment_questionnaire_question_19_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>financial_markets</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Financial markets</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>financial_services_pre_employment_assessment_questionnaire_question_19_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>financial_services</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Financial services</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>financial_services_pre_employment_assessment_questionnaire_question_19_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>financial_services</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
